--- a/data/data_statics_nested.xlsx
+++ b/data/data_statics_nested.xlsx
@@ -37,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -76,6 +76,27 @@
       <left/>
       <right style="thin"/>
       <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
       <bottom style="thin"/>
       <diagonal/>
     </border>
@@ -453,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,231 +597,2424 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>X-Topic</t>
+          <t>20NG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>351</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>518</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>DBPedia</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>736</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>TREC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>531</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>435</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>468</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>banking</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>472</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>704</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>clinc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>457</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>1,345</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1,801</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2,250</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>ecdt</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>hwu</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>557</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1,032</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t>mcid</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>stackoverflow</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>1,200</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>5,991</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t>thucnews</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1,421</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t>20NG</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1,750</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2,581</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>3,498</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>496</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n"/>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t>DBPedia</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1,204</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2,315</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>3,111</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>3,517</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t>TREC</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1,610</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>582</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2,176</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2,343</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2,426</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1,750</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2,800</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>banking</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1,150</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2,368</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>3,522</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>391</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>4,498</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>clinc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2,280</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>1,767</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>X-Topic</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>6,722</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>9,002</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1,200</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2,250</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t>ecdt</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>684</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>1,046</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>hwu</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1,808</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2,784</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>3,853</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>451</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>1,032</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>mcid</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2,657</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>378</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>595</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t>stackoverflow</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1,500</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>3,000</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>4,500</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>750</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>6,000</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>5,991</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n"/>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t>thucnews</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1,750</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2,500</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>504</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>1,421</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t>20NG</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1,825</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>3,505</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>5,166</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t>DBPedia</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2,387</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>4,603</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>661</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>6,195</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n"/>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t>TREC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3,224</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2,917</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>415</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2,970</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>432</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2,982</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1,767</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>X-Topic</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>4,350</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>4,683</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>513</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>4,849</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>490</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t>Yahoo</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1,400</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>5,600</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>800</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t>banking</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2,303</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>4,740</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>7,048</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>783</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>9,003</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>3,080</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n"/>
+      <c r="B31" s="1" t="inlineStr">
+        <is>
+          <t>clinc</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>4,560</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>9,000</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>1,125</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>13,440</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>1,680</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>18,000</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2,250</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2,250</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n"/>
+      <c r="B32" s="1" t="inlineStr">
+        <is>
+          <t>ecdt</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,372</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>1,879</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2,099</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>770</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n"/>
+      <c r="B33" s="1" t="inlineStr">
+        <is>
+          <t>hwu</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1,886</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>3,616</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>5,575</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>7,712</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>1,032</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n"/>
+      <c r="B34" s="1" t="inlineStr">
+        <is>
+          <t>mcid</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>601</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>5,318</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>756</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>5,836</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>5,937</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>849</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>5,954</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>866</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>1,767</t>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>905</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>1,198</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n"/>
+      <c r="B35" s="1" t="inlineStr">
+        <is>
+          <t>stackoverflow</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2,999</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>5,997</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>8,997</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>1,498</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>11,996</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>1,998</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>5,991</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n"/>
+      <c r="B36" s="1" t="inlineStr">
+        <is>
+          <t>thucnews</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>3,500</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>502</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>1,421</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="7">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="L1:O1"/>
+    <mergeCell ref="A4:A14"/>
+    <mergeCell ref="A26:A36"/>
+    <mergeCell ref="A15:A25"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
+    <mergeCell ref="L1:O1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
